--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0003T0006Z000C1N44_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0003T0006Z000C1N44_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>77.7283530133187</v>
+        <v>12.63085736466429</v>
       </c>
       <c r="D2" t="n">
-        <v>67.07520215224231</v>
+        <v>10.89972034973938</v>
       </c>
       <c r="E2" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F2" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>81.65487671381663</v>
+        <v>13.2689174659952</v>
       </c>
       <c r="D3" t="n">
-        <v>57.26279575586382</v>
+        <v>9.305204310327872</v>
       </c>
       <c r="E3" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F3" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>93.99651758322649</v>
+        <v>15.27443410727431</v>
       </c>
       <c r="D4" t="n">
-        <v>87.51160543071686</v>
+        <v>14.22063588249149</v>
       </c>
       <c r="E4" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F4" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>75.99791875608922</v>
+        <v>12.3496617978645</v>
       </c>
       <c r="D5" t="n">
-        <v>64.67012561757004</v>
+        <v>10.50889541285513</v>
       </c>
       <c r="E5" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F5" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>85.49425924554417</v>
+        <v>13.89281712740093</v>
       </c>
       <c r="D6" t="n">
-        <v>52.88374995573183</v>
+        <v>8.593609367806422</v>
       </c>
       <c r="E6" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F6" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>72.73971950557014</v>
+        <v>11.82020441965515</v>
       </c>
       <c r="D7" t="n">
-        <v>63.33673181183065</v>
+        <v>10.29221891942248</v>
       </c>
       <c r="E7" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F7" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>76.02733697179211</v>
+        <v>12.35444225791622</v>
       </c>
       <c r="D8" t="n">
-        <v>68.02965773150531</v>
+        <v>11.05481938136961</v>
       </c>
       <c r="E8" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F8" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>98.89758383337553</v>
+        <v>16.07085737292352</v>
       </c>
       <c r="D9" t="n">
-        <v>59.60075502877459</v>
+        <v>9.685122692175872</v>
       </c>
       <c r="E9" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F9" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>65.15112655841502</v>
+        <v>10.58705806574244</v>
       </c>
       <c r="D10" t="n">
-        <v>52.74569309990693</v>
+        <v>8.571175128734877</v>
       </c>
       <c r="E10" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F10" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>88.02255233896895</v>
+        <v>14.30366475508245</v>
       </c>
       <c r="D11" t="n">
-        <v>51.36576589431771</v>
+        <v>8.346936957826628</v>
       </c>
       <c r="E11" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F11" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>77.67673558350592</v>
+        <v>12.62246953231971</v>
       </c>
       <c r="D12" t="n">
-        <v>43.06390600026895</v>
+        <v>6.997884725043705</v>
       </c>
       <c r="E12" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F12" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>48.06711810120562</v>
+        <v>7.810906691445913</v>
       </c>
       <c r="D13" t="n">
-        <v>36.2210613241345</v>
+        <v>5.885922465171857</v>
       </c>
       <c r="E13" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F13" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>74.66113717565905</v>
+        <v>12.1324347910446</v>
       </c>
       <c r="D14" t="n">
-        <v>34.44198019858905</v>
+        <v>5.59682178227072</v>
       </c>
       <c r="E14" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F14" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>73.70768404653681</v>
+        <v>11.97749865756223</v>
       </c>
       <c r="D15" t="n">
-        <v>68.85477877334272</v>
+        <v>11.18890155066819</v>
       </c>
       <c r="E15" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F15" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>46.71055018022397</v>
+        <v>7.590464404286395</v>
       </c>
       <c r="D16" t="n">
-        <v>38.78307863242186</v>
+        <v>6.302250277768553</v>
       </c>
       <c r="E16" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F16" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>42.72246873082543</v>
+        <v>6.942401168759133</v>
       </c>
       <c r="D17" t="n">
-        <v>33.08597814956328</v>
+        <v>5.376471449304034</v>
       </c>
       <c r="E17" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F17" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>42.27986770509909</v>
+        <v>6.870478502078603</v>
       </c>
       <c r="D18" t="n">
-        <v>29.15485069297717</v>
+        <v>4.73766323760879</v>
       </c>
       <c r="E18" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F18" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>41.85498897048934</v>
+        <v>6.801435707704518</v>
       </c>
       <c r="D19" t="n">
-        <v>36.15908695142893</v>
+        <v>5.875851629607202</v>
       </c>
       <c r="E19" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F19" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>59.52859184879007</v>
+        <v>9.673396175428387</v>
       </c>
       <c r="D20" t="n">
-        <v>54.49745444896339</v>
+        <v>8.855836347956551</v>
       </c>
       <c r="E20" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F20" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>50.99922160880092</v>
+        <v>8.28737351143015</v>
       </c>
       <c r="D21" t="n">
-        <v>46.49605439814896</v>
+        <v>7.555608839699206</v>
       </c>
       <c r="E21" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F21" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>73.42875009474255</v>
+        <v>11.93217189039567</v>
       </c>
       <c r="D22" t="n">
-        <v>67.8248050074593</v>
+        <v>11.02153081371214</v>
       </c>
       <c r="E22" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F22" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>37.82470042058942</v>
+        <v>6.146513818345781</v>
       </c>
       <c r="D23" t="n">
-        <v>33.47315149608322</v>
+        <v>5.439387118113523</v>
       </c>
       <c r="E23" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F23" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>28.38141779057787</v>
+        <v>4.611980390968904</v>
       </c>
       <c r="D24" t="n">
-        <v>23.28648796065972</v>
+        <v>3.784054293607205</v>
       </c>
       <c r="E24" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F24" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>42.87383296053422</v>
+        <v>6.966997856086811</v>
       </c>
       <c r="D25" t="n">
-        <v>11.84937967875673</v>
+        <v>1.925524197797969</v>
       </c>
       <c r="E25" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F25" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>61.02200409843762</v>
+        <v>9.916075665996113</v>
       </c>
       <c r="D26" t="n">
-        <v>55.40646270280639</v>
+        <v>9.00355018920604</v>
       </c>
       <c r="E26" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F26" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>25.09648649999479</v>
+        <v>4.078179056249153</v>
       </c>
       <c r="D27" t="n">
-        <v>12.74709951915948</v>
+        <v>2.071403671863415</v>
       </c>
       <c r="E27" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F27" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>28.94220705225631</v>
+        <v>4.703108645991651</v>
       </c>
       <c r="D28" t="n">
-        <v>24.54737560077834</v>
+        <v>3.98894853512648</v>
       </c>
       <c r="E28" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F28" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>18.79947736105441</v>
+        <v>3.054915071171342</v>
       </c>
       <c r="D29" t="n">
-        <v>8.727291670229631</v>
+        <v>1.418184896412315</v>
       </c>
       <c r="E29" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F29" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>61.95605047435913</v>
+        <v>10.06785820208336</v>
       </c>
       <c r="D30" t="n">
-        <v>56.00801575465034</v>
+        <v>9.101302560130682</v>
       </c>
       <c r="E30" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F30" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>9.549673575711786</v>
+        <v>1.551821956053165</v>
       </c>
       <c r="D31" t="n">
-        <v>5.190976384810898</v>
+        <v>0.843533662531771</v>
       </c>
       <c r="E31" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F31" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>13.24472312336638</v>
+        <v>2.152267507547037</v>
       </c>
       <c r="D32" t="n">
-        <v>6.394909691656856</v>
+        <v>1.039172824894239</v>
       </c>
       <c r="E32" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F32" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>29.29245516555412</v>
+        <v>4.760023964402544</v>
       </c>
       <c r="D33" t="n">
-        <v>12.99565112338698</v>
+        <v>2.111793307550384</v>
       </c>
       <c r="E33" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F33" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>27.31292985978272</v>
+        <v>4.438351102214693</v>
       </c>
       <c r="D34" t="n">
-        <v>21.32398195104019</v>
+        <v>3.465147067044031</v>
       </c>
       <c r="E34" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F34" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1536,16 +1536,16 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>40.35699255050582</v>
+        <v>6.558011289457196</v>
       </c>
       <c r="D35" t="n">
-        <v>11.90751466119196</v>
+        <v>1.934971132443694</v>
       </c>
       <c r="E35" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F35" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1568,16 +1568,16 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>15.68657310307379</v>
+        <v>2.549068129249491</v>
       </c>
       <c r="D36" t="n">
-        <v>12.5714028704964</v>
+        <v>2.042852966455666</v>
       </c>
       <c r="E36" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F36" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1600,16 +1600,16 @@
         <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>2.770773158309536</v>
+        <v>0.4502506382252996</v>
       </c>
       <c r="D37" t="n">
-        <v>4.674599845441048</v>
+        <v>0.7596224748841702</v>
       </c>
       <c r="E37" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F37" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1632,16 +1632,16 @@
         <v>37</v>
       </c>
       <c r="C38" t="n">
-        <v>78.235587750837</v>
+        <v>12.71328300951101</v>
       </c>
       <c r="D38" t="n">
-        <v>45.60724757147886</v>
+        <v>7.411177730365314</v>
       </c>
       <c r="E38" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F38" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1664,16 +1664,16 @@
         <v>38</v>
       </c>
       <c r="C39" t="n">
-        <v>29.26917438018979</v>
+        <v>4.756240836780841</v>
       </c>
       <c r="D39" t="n">
-        <v>26.32235280306164</v>
+        <v>4.277382330497517</v>
       </c>
       <c r="E39" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F39" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1696,16 +1696,16 @@
         <v>39</v>
       </c>
       <c r="C40" t="n">
-        <v>41.07660747078005</v>
+        <v>6.674948714001758</v>
       </c>
       <c r="D40" t="n">
-        <v>22.51341605553273</v>
+        <v>3.658430109024069</v>
       </c>
       <c r="E40" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F40" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1728,16 +1728,16 @@
         <v>40</v>
       </c>
       <c r="C41" t="n">
-        <v>50.93546574192913</v>
+        <v>8.277013183063485</v>
       </c>
       <c r="D41" t="n">
-        <v>45.10449325320451</v>
+        <v>7.329480153645733</v>
       </c>
       <c r="E41" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F41" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1760,16 +1760,16 @@
         <v>41</v>
       </c>
       <c r="C42" t="n">
-        <v>14.32465322384639</v>
+        <v>2.327756148875038</v>
       </c>
       <c r="D42" t="n">
-        <v>12.38978899180926</v>
+        <v>2.013340711169005</v>
       </c>
       <c r="E42" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F42" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1792,16 +1792,16 @@
         <v>42</v>
       </c>
       <c r="C43" t="n">
-        <v>49.49553005227258</v>
+        <v>8.043023633494295</v>
       </c>
       <c r="D43" t="n">
-        <v>37.99789833369442</v>
+        <v>6.174658479225344</v>
       </c>
       <c r="E43" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F43" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>43</v>
       </c>
       <c r="C44" t="n">
-        <v>19.45724108284884</v>
+        <v>3.161801675962936</v>
       </c>
       <c r="D44" t="n">
-        <v>20.27119329473086</v>
+        <v>3.294068910393765</v>
       </c>
       <c r="E44" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F44" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1856,16 +1856,16 @@
         <v>44</v>
       </c>
       <c r="C45" t="n">
-        <v>62.34092950316911</v>
+        <v>10.13040104426498</v>
       </c>
       <c r="D45" t="n">
-        <v>46.51075144523038</v>
+        <v>7.557997109849937</v>
       </c>
       <c r="E45" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F45" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1888,16 +1888,16 @@
         <v>45</v>
       </c>
       <c r="C46" t="n">
-        <v>75.33718950279564</v>
+        <v>12.24229329420429</v>
       </c>
       <c r="D46" t="n">
-        <v>57.01973342624463</v>
+        <v>9.265706681764753</v>
       </c>
       <c r="E46" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F46" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1920,16 +1920,16 @@
         <v>46</v>
       </c>
       <c r="C47" t="n">
-        <v>41.50894154592313</v>
+        <v>6.745203001212508</v>
       </c>
       <c r="D47" t="n">
-        <v>39.40246265939159</v>
+        <v>6.402900182151133</v>
       </c>
       <c r="E47" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F47" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1952,16 +1952,16 @@
         <v>47</v>
       </c>
       <c r="C48" t="n">
-        <v>84.77157421455857</v>
+        <v>13.77538080986577</v>
       </c>
       <c r="D48" t="n">
-        <v>64.37671249070669</v>
+        <v>10.46121577973984</v>
       </c>
       <c r="E48" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F48" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -1984,16 +1984,16 @@
         <v>48</v>
       </c>
       <c r="C49" t="n">
-        <v>29.40412273014019</v>
+        <v>4.778169943647781</v>
       </c>
       <c r="D49" t="n">
-        <v>28.58308515006748</v>
+        <v>4.644751336885966</v>
       </c>
       <c r="E49" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F49" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2016,16 +2016,16 @@
         <v>49</v>
       </c>
       <c r="C50" t="n">
-        <v>55.75321604322247</v>
+        <v>9.059897607023652</v>
       </c>
       <c r="D50" t="n">
-        <v>51.44963042911228</v>
+        <v>8.360564944730747</v>
       </c>
       <c r="E50" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F50" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2048,16 +2048,16 @@
         <v>50</v>
       </c>
       <c r="C51" t="n">
-        <v>42.31219000616616</v>
+        <v>6.875730876002002</v>
       </c>
       <c r="D51" t="n">
-        <v>41.77667016568368</v>
+        <v>6.788708901923599</v>
       </c>
       <c r="E51" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F51" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2080,16 +2080,16 @@
         <v>51</v>
       </c>
       <c r="C52" t="n">
-        <v>45.88924070090265</v>
+        <v>7.457001613896682</v>
       </c>
       <c r="D52" t="n">
-        <v>44.7886210276358</v>
+        <v>7.278150916990818</v>
       </c>
       <c r="E52" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F52" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2112,16 +2112,16 @@
         <v>52</v>
       </c>
       <c r="C53" t="n">
-        <v>61.96020819241565</v>
+        <v>10.06853383126754</v>
       </c>
       <c r="D53" t="n">
-        <v>58.22578491117165</v>
+        <v>9.461690048065394</v>
       </c>
       <c r="E53" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F53" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2144,16 +2144,16 @@
         <v>53</v>
       </c>
       <c r="C54" t="n">
-        <v>48.32721958555736</v>
+        <v>7.853173182653071</v>
       </c>
       <c r="D54" t="n">
-        <v>48.56234178555996</v>
+        <v>7.891380540153493</v>
       </c>
       <c r="E54" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F54" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2176,16 +2176,16 @@
         <v>54</v>
       </c>
       <c r="C55" t="n">
-        <v>81.30485398548129</v>
+        <v>13.21203877264071</v>
       </c>
       <c r="D55" t="n">
-        <v>76.38572414788565</v>
+        <v>12.41268017403142</v>
       </c>
       <c r="E55" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F55" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2208,16 +2208,16 @@
         <v>55</v>
       </c>
       <c r="C56" t="n">
-        <v>69.74617590324527</v>
+        <v>11.33375358427736</v>
       </c>
       <c r="D56" t="n">
-        <v>68.13283825288065</v>
+        <v>11.07158621609311</v>
       </c>
       <c r="E56" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F56" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2240,16 +2240,16 @@
         <v>56</v>
       </c>
       <c r="C57" t="n">
-        <v>60.00496874366154</v>
+        <v>9.750807420845</v>
       </c>
       <c r="D57" t="n">
-        <v>58.23021460967407</v>
+        <v>9.462409874072037</v>
       </c>
       <c r="E57" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F57" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2272,16 +2272,16 @@
         <v>57</v>
       </c>
       <c r="C58" t="n">
-        <v>64.89290559041241</v>
+        <v>10.54509715844202</v>
       </c>
       <c r="D58" t="n">
-        <v>62.37883690179713</v>
+        <v>10.13656099654203</v>
       </c>
       <c r="E58" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F58" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2304,16 +2304,16 @@
         <v>58</v>
       </c>
       <c r="C59" t="n">
-        <v>60.43220983695495</v>
+        <v>9.82023409850518</v>
       </c>
       <c r="D59" t="n">
-        <v>59.65401041255174</v>
+        <v>9.693776692039659</v>
       </c>
       <c r="E59" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F59" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2336,16 +2336,16 @@
         <v>59</v>
       </c>
       <c r="C60" t="n">
-        <v>65.40242572050046</v>
+        <v>10.62789417958133</v>
       </c>
       <c r="D60" t="n">
-        <v>64.8246309579004</v>
+        <v>10.53400253065882</v>
       </c>
       <c r="E60" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F60" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2368,16 +2368,16 @@
         <v>60</v>
       </c>
       <c r="C61" t="n">
-        <v>76.7718924178191</v>
+        <v>12.47543251789561</v>
       </c>
       <c r="D61" t="n">
-        <v>74.10239858989506</v>
+        <v>12.04163977085795</v>
       </c>
       <c r="E61" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F61" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2400,16 +2400,16 @@
         <v>61</v>
       </c>
       <c r="C62" t="n">
-        <v>85.33811683688739</v>
+        <v>13.8674439859942</v>
       </c>
       <c r="D62" t="n">
-        <v>84.20160173862321</v>
+        <v>13.68276028252627</v>
       </c>
       <c r="E62" t="n">
-        <v>23.41393980940847</v>
+        <v>3.804765219028877</v>
       </c>
       <c r="F62" t="n">
-        <v>21.26730745529827</v>
+        <v>3.455937461485969</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
